--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="270" yWindow="225" windowWidth="19200" windowHeight="7980" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="General" sheetId="1" r:id="rId1"/>
-    <sheet name="Sword" sheetId="2" r:id="rId2"/>
-    <sheet name="Archery" sheetId="3" r:id="rId3"/>
-    <sheet name="Fire" sheetId="4" r:id="rId4"/>
-    <sheet name="Ice" sheetId="5" r:id="rId5"/>
-    <sheet name="Poison" sheetId="6" r:id="rId6"/>
-    <sheet name="Support" sheetId="7" r:id="rId7"/>
-    <sheet name="Enhancement" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="General" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sword" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Archery" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Fire" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Ice" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Poison" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Support" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Enhancement" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -41,7 +41,7 @@
     <t>slash</t>
   </si>
   <si>
-    <t>thrust</t>
+    <t>dash</t>
   </si>
   <si>
     <t>swordmastery</t>
@@ -122,44 +122,37 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="1"/>
+      <scheme val="major"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="major"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -201,7 +194,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -500,9 +493,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" style="1" customWidth="1"/>
@@ -510,11 +503,10 @@
     <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -528,14 +520,14 @@
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" ht="35.450000000000003" customHeight="1">
+    <row r="2" ht="35.45" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -546,23 +538,22 @@
       <c r="D3" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -574,12 +565,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="38.450000000000003" customHeight="1">
+    <row r="2" ht="38.45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -588,15 +579,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -604,7 +594,7 @@
     <col min="4" max="4" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -614,13 +604,13 @@
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="1" t="s">
@@ -629,24 +619,22 @@
       <c r="D3" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="4" customWidth="1"/>
     <col min="2" max="2" width="17" style="4" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="4"/>
+    <col min="4" max="16384" width="8.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -654,52 +642,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:3" ht="40.9" customHeight="1">
+    <row r="3" ht="40.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="5"/>
     </row>
-    <row r="4" spans="1:3" ht="40.9" customHeight="1">
+    <row r="4" ht="40.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1">
+    <row r="6" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="4" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="4" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="4"/>
+    <col min="4" max="16384" width="8.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>18</v>
       </c>
@@ -707,43 +693,41 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="40.15" customHeight="1">
+    <row r="2" ht="40.15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1">
+    <row r="4" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="4" customWidth="1"/>
     <col min="2" max="2" width="18.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="4"/>
+    <col min="4" max="16384" width="8.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
@@ -751,42 +735,40 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="46.9" customHeight="1">
+    <row r="2" ht="46.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="4" customWidth="1"/>
     <col min="2" max="2" width="9.42578125" style="4" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="4"/>
+    <col min="6" max="16384" width="8.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
@@ -797,46 +779,44 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.15" customHeight="1">
+    <row r="2" ht="43.15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
       <c r="D3" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="4"/>
+    <col min="6" max="16384" width="8.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>29</v>
       </c>
@@ -847,22 +827,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>